--- a/02_DIA_inicio_2026_analisis_assets/rbd_9699_colegio-naciones-unidas_nt2_rubricas.xlsx
+++ b/02_DIA_inicio_2026_analisis_assets/rbd_9699_colegio-naciones-unidas_nt2_rubricas.xlsx
@@ -1992,13 +1992,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{02A025AD-320C-4F3C-82F2-FDF0CFF8D84C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{79EA4A81-CC68-46A6-AB0C-1F3C5B11A505}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D0612723-405F-4473-BD2B-A956C6DE2DA9}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{ABF7ED3A-4E66-40E8-8849-5D61AF45E182}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F92FA20B-E9F4-4A23-A94E-8E73A1170303}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EACADC0A-23E9-4B92-A14B-CADEB61221F9}"/>
 </file>